--- a/bench/results/3090/elementwise.xlsx
+++ b/bench/results/3090/elementwise.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.019255</t>
+          <t>0.021623</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.024615</t>
+          <t>0.028310</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -496,7 +496,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.018191</t>
+          <t>0.022017</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -517,7 +517,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.020813</t>
+          <t>0.022530</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -538,7 +538,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.024996</t>
+          <t>0.029269</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -559,7 +559,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.018591</t>
+          <t>0.021644</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.019205</t>
+          <t>0.022647</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.024750</t>
+          <t>0.029023</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -622,7 +622,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.018230</t>
+          <t>0.020757</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -643,7 +643,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.019232</t>
+          <t>0.021331</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.024882</t>
+          <t>0.028265</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -685,7 +685,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.018179</t>
+          <t>0.020646</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.019139</t>
+          <t>0.021198</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.025582</t>
+          <t>0.028437</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.018138</t>
+          <t>0.020515</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.019178</t>
+          <t>0.021364</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -790,7 +790,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.036026</t>
+          <t>0.036996</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.018713</t>
+          <t>0.020801</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.019295</t>
+          <t>0.021433</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.057591</t>
+          <t>0.058046</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -874,7 +874,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.024922</t>
+          <t>0.025318</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -895,7 +895,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.018991</t>
+          <t>0.021369</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.100557</t>
+          <t>0.099597</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -937,7 +937,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.038838</t>
+          <t>0.038757</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.019222</t>
+          <t>0.021043</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.186700</t>
+          <t>0.182524</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.065743</t>
+          <t>0.064975</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.019129</t>
+          <t>0.021315</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.358337</t>
+          <t>0.345366</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.119564</t>
+          <t>0.117304</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.019021</t>
+          <t>0.021132</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.805197</t>
+          <t>0.739894</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.227359</t>
+          <t>0.222045</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.024493</t>
+          <t>0.025035</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2.463232</t>
+          <t>2.395108</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.464801</t>
+          <t>0.452747</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.040226</t>
+          <t>0.040615</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5.192040</t>
+          <t>5.096004</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.965663</t>
+          <t>0.948128</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.070962</t>
+          <t>0.070464</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>10.370300</t>
+          <t>10.189117</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1.901702</t>
+          <t>1.873276</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.130019</t>
+          <t>0.130284</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>20.713027</t>
+          <t>20.461418</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.777545</t>
+          <t>3.750000</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1386,6 +1386,195 @@
       </c>
       <c r="E46" t="n">
         <v>201326592</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>residual_add</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>33554432</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.248359</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>33554432</v>
+      </c>
+      <c r="E47" t="n">
+        <v>201326592</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>rmsnorm</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>33554432</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>62.768216</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>134217728</v>
+      </c>
+      <c r="E48" t="n">
+        <v>268435456</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>softmax</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>33554432</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7.487554</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>167772160</v>
+      </c>
+      <c r="E49" t="n">
+        <v>402653184</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>residual_add</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>67108864</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.485257</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>67108864</v>
+      </c>
+      <c r="E50" t="n">
+        <v>402653184</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>rmsnorm</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>67108864</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>125.175273</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>268435456</v>
+      </c>
+      <c r="E51" t="n">
+        <v>536870912</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>softmax</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>67108864</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>14.946053</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>335544320</v>
+      </c>
+      <c r="E52" t="n">
+        <v>805306368</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>residual_add</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>134217728</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0.961377</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>134217728</v>
+      </c>
+      <c r="E53" t="n">
+        <v>805306368</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>rmsnorm</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>134217728</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>249.943790</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>536870912</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1073741824</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>softmax</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>134217728</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>29.836482</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>671088640</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1610612736</v>
       </c>
     </row>
   </sheetData>
